--- a/artfynd/A 2254-2025 artfynd.xlsx
+++ b/artfynd/A 2254-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>62344055</v>
       </c>
       <c r="B2" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575436.1466185818</v>
+        <v>575436</v>
       </c>
       <c r="R2" t="n">
-        <v>6895813.175545356</v>
+        <v>6895813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2016-08-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,19 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105705961</v>
+        <v>62344056</v>
       </c>
       <c r="B3" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -833,7 +813,12 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575463.5438620161</v>
+        <v>575349</v>
       </c>
       <c r="R3" t="n">
-        <v>6895822.19643821</v>
+        <v>6895787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,27 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Blommar i mitten av augusti</t>
+          <t>ny lokal, västra fläcken  0-10 m öst om jaktpass, vägkantsslåtter, blommar i mitten av augusti</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,18 +879,227 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105705961</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kölsjön, vägkant 1 km V om, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575463</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6895822</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blommar i mitten av augusti</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Emma Hellkvist</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Emma Hellkvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105705962</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kölsjön, vägkant 1 km V om, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575351</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6895790</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Blommar i mitten av augusti</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2254-2025 artfynd.xlsx
+++ b/artfynd/A 2254-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62344055</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62344056</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105705961</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105705962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>